--- a/SPRB.xlsx
+++ b/SPRB.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Martin Shkreli - DL\models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17E85A81-B5FE-4D29-82A5-D79C20D67EA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEE064CF-4499-47C7-9795-D27B810716EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3210" yWindow="1830" windowWidth="26040" windowHeight="16240" activeTab="3" xr2:uid="{8EF78811-AEFC-40C2-88C2-7B926EB4226D}"/>
+    <workbookView xWindow="5780" yWindow="4160" windowWidth="23600" windowHeight="13830" xr2:uid="{8EF78811-AEFC-40C2-88C2-7B926EB4226D}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="69">
   <si>
     <t>Price</t>
   </si>
@@ -77,9 +77,6 @@
     <t>BLA Q126</t>
   </si>
   <si>
-    <t>Q125</t>
-  </si>
-  <si>
     <t>Main</t>
   </si>
   <si>
@@ -243,6 +240,12 @@
   </si>
   <si>
     <t>https://pubmed.ncbi.nlm.nih.gov/31590383/</t>
+  </si>
+  <si>
+    <t>Q425</t>
+  </si>
+  <si>
+    <t>BLA Q426</t>
   </si>
 </sst>
 </file>
@@ -787,7 +790,7 @@
         <v>0</v>
       </c>
       <c r="J2" s="2">
-        <v>46</v>
+        <v>60</v>
       </c>
     </row>
     <row r="3" spans="2:11" x14ac:dyDescent="0.25">
@@ -807,16 +810,18 @@
         <v>1</v>
       </c>
       <c r="J3" s="3">
-        <v>0.7</v>
+        <v>1.3720000000000001</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>12</v>
+        <v>67</v>
       </c>
     </row>
     <row r="4" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B4" s="5"/>
       <c r="C4" s="10"/>
-      <c r="D4" s="10"/>
+      <c r="D4" s="10" t="s">
+        <v>68</v>
+      </c>
       <c r="E4" s="10"/>
       <c r="F4" s="10"/>
       <c r="G4" s="11"/>
@@ -825,7 +830,7 @@
       </c>
       <c r="J4" s="3">
         <f>+J2*J3</f>
-        <v>32.199999999999996</v>
+        <v>82.320000000000007</v>
       </c>
     </row>
     <row r="5" spans="2:11" x14ac:dyDescent="0.25">
@@ -839,10 +844,10 @@
         <v>3</v>
       </c>
       <c r="J5" s="3">
-        <v>25.614999999999998</v>
+        <v>48.905999999999999</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>12</v>
+        <v>67</v>
       </c>
     </row>
     <row r="6" spans="2:11" x14ac:dyDescent="0.25">
@@ -859,7 +864,7 @@
         <v>0</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>12</v>
+        <v>67</v>
       </c>
     </row>
     <row r="7" spans="2:11" x14ac:dyDescent="0.25">
@@ -868,7 +873,7 @@
       </c>
       <c r="J7" s="3">
         <f>+J4-J5+J6</f>
-        <v>6.5849999999999973</v>
+        <v>33.414000000000009</v>
       </c>
     </row>
   </sheetData>
@@ -888,7 +893,7 @@
   <sheetData>
     <row r="1" spans="1:44" x14ac:dyDescent="0.35">
       <c r="A1" s="21" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="2" spans="1:44" x14ac:dyDescent="0.35">
@@ -953,7 +958,7 @@
     </row>
     <row r="3" spans="1:44" x14ac:dyDescent="0.35">
       <c r="B3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C3">
         <v>500</v>
@@ -1081,7 +1086,7 @@
     </row>
     <row r="5" spans="1:44" x14ac:dyDescent="0.35">
       <c r="B5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C5" s="15">
         <f>+C3*C4</f>
@@ -1146,7 +1151,7 @@
     </row>
     <row r="6" spans="1:44" x14ac:dyDescent="0.35">
       <c r="B6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C6" s="16">
         <v>0</v>
@@ -1184,7 +1189,7 @@
     </row>
     <row r="7" spans="1:44" s="17" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B7" s="17" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D7" s="17">
         <f>+D5*D6</f>
@@ -1229,7 +1234,7 @@
     </row>
     <row r="8" spans="1:44" x14ac:dyDescent="0.35">
       <c r="B8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D8" s="18">
         <f>+D7*0.1</f>
@@ -1274,7 +1279,7 @@
     </row>
     <row r="9" spans="1:44" x14ac:dyDescent="0.35">
       <c r="B9" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D9" s="15">
         <f>+D7-D8</f>
@@ -1319,7 +1324,7 @@
     </row>
     <row r="10" spans="1:44" x14ac:dyDescent="0.35">
       <c r="B10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D10">
         <v>50</v>
@@ -1354,7 +1359,7 @@
     </row>
     <row r="11" spans="1:44" x14ac:dyDescent="0.35">
       <c r="B11" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D11" s="15">
         <f>+D9-D10</f>
@@ -1399,7 +1404,7 @@
     </row>
     <row r="12" spans="1:44" x14ac:dyDescent="0.35">
       <c r="B12" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D12" s="15">
         <v>0</v>
@@ -1443,7 +1448,7 @@
     </row>
     <row r="13" spans="1:44" x14ac:dyDescent="0.35">
       <c r="B13" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D13" s="15">
         <f>+D11-D12</f>
@@ -1612,7 +1617,7 @@
     </row>
     <row r="15" spans="1:44" x14ac:dyDescent="0.35">
       <c r="B15" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C15" s="16">
         <v>0.09</v>
@@ -1620,7 +1625,7 @@
     </row>
     <row r="16" spans="1:44" x14ac:dyDescent="0.35">
       <c r="B16" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C16" s="15">
         <f>NPV(C15,D13:BZ13)</f>
@@ -1700,20 +1705,20 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" s="14" t="s">
         <v>14</v>
-      </c>
-      <c r="C3" s="14" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -1721,7 +1726,7 @@
         <v>8</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -1734,19 +1739,20 @@
   <dimension ref="A1:G23"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
+    <col min="1" max="1" width="4.7265625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="11.7265625" customWidth="1"/>
     <col min="4" max="4" width="12.36328125" customWidth="1"/>
     <col min="5" max="5" width="9.81640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
-        <v>13</v>
+      <c r="A1" s="21" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="2" spans="1:7" s="20" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B2" s="20" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C2" s="17">
         <f>SUM(C3:C20)</f>
@@ -1755,7 +1761,7 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C3" s="15">
         <v>135</v>
@@ -1768,15 +1774,15 @@
         <v>2444444.4444444445</v>
       </c>
       <c r="F3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C4" s="15">
         <v>24</v>
@@ -1789,12 +1795,12 @@
         <v>755833.33333333337</v>
       </c>
       <c r="F4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C5" s="15">
         <v>11</v>
@@ -1807,22 +1813,22 @@
         <v>10590909.090909092</v>
       </c>
       <c r="F5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C6" s="15"/>
       <c r="D6" s="15"/>
       <c r="F6" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B7" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C7" s="15">
         <v>8</v>
@@ -1835,12 +1841,12 @@
         <v>10690000</v>
       </c>
       <c r="F7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B8" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C8" s="15">
         <v>110</v>
@@ -1853,15 +1859,15 @@
         <v>1927272.7272727273</v>
       </c>
       <c r="F8" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G8" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B9" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C9">
         <v>14</v>
@@ -1876,7 +1882,7 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B10" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C10">
         <v>1</v>
@@ -1891,7 +1897,7 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B11" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C11" s="15">
         <v>14</v>
@@ -1904,12 +1910,12 @@
         <v>3696428.5714285714</v>
       </c>
       <c r="F11" s="22" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B12" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C12" s="15">
         <v>5</v>
@@ -1917,15 +1923,15 @@
       <c r="D12" s="15"/>
       <c r="E12" s="15"/>
       <c r="F12" s="22" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G12" s="22" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B13" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C13" s="15">
         <f t="shared" ref="C13:C14" si="0">+D13/E13</f>
@@ -1939,12 +1945,12 @@
         <v>4780700.3066378068</v>
       </c>
       <c r="F13" s="22" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B14" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C14" s="15">
         <f t="shared" si="0"/>
@@ -1958,15 +1964,15 @@
         <v>4780700.3066378068</v>
       </c>
       <c r="F14" s="22" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B15" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C15" s="15">
-        <f>+D15/E15</f>
+        <f t="shared" ref="C15:C20" si="1">+D15/E15</f>
         <v>8.6368099549495962</v>
       </c>
       <c r="D15" s="15">
@@ -1979,10 +1985,10 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B16" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C16" s="15">
-        <f>+D16/E16</f>
+        <f t="shared" si="1"/>
         <v>25.937622533634052</v>
       </c>
       <c r="D16" s="15">
@@ -1995,10 +2001,10 @@
     </row>
     <row r="17" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B17" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C17" s="15">
-        <f>+D17/E17</f>
+        <f t="shared" si="1"/>
         <v>14.328444706080102</v>
       </c>
       <c r="D17" s="15">
@@ -2011,10 +2017,10 @@
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B18" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C18" s="15">
-        <f>+D18/E18</f>
+        <f t="shared" si="1"/>
         <v>17.468152078901451</v>
       </c>
       <c r="D18" s="15">
@@ -2027,10 +2033,10 @@
     </row>
     <row r="19" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B19" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C19" s="15">
-        <f>+D19/E19</f>
+        <f t="shared" si="1"/>
         <v>12.339196397250587</v>
       </c>
       <c r="D19" s="15">
@@ -2041,18 +2047,18 @@
         <v>4780700.3066378068</v>
       </c>
       <c r="F19" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G19" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B20" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C20" s="15">
-        <f>+D20/E20</f>
+        <f t="shared" si="1"/>
         <v>27.380925723005625</v>
       </c>
       <c r="D20" s="15">
@@ -2063,21 +2069,21 @@
         <v>4780700.3066378068</v>
       </c>
       <c r="F20" s="21" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G20" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="22" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B22" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C22">
         <v>15</v>
       </c>
       <c r="F22" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.35">
@@ -2085,12 +2091,13 @@
         <v>65</v>
       </c>
       <c r="F23" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="F20" r:id="rId1" xr:uid="{494B32F2-C605-428E-A8D1-CFCD8ED4EF27}"/>
+    <hyperlink ref="A1" location="Main!A1" display="Main" xr:uid="{BF235CD3-91BC-4770-A263-C1290CAD3CB8}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
